--- a/public/assets/template_excel/template_unggah_excel_presensi_pegawai_shift.xlsx
+++ b/public/assets/template_excel/template_unggah_excel_presensi_pegawai_shift.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\neosimpeg\public\assets\template_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D168DB-F579-424A-86B1-1DD836520425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA90CD8-EA5A-4CF4-B33E-BBEA610A9601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{A1702C02-858C-4123-9DA9-AD5506EBDB66}"/>
   </bookViews>
@@ -44,10 +44,10 @@
     <t>nama</t>
   </si>
   <si>
-    <t>tanggal</t>
+    <t>kode shift</t>
   </si>
   <si>
-    <t>kode shift</t>
+    <t>tanggal (d-m-Y)</t>
   </si>
 </sst>
 </file>
@@ -427,7 +427,7 @@
   <cols>
     <col min="1" max="1" width="19.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="16384" width="8.88671875" style="1"/>
   </cols>
@@ -440,10 +440,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
